--- a/artfynd/A 5104-2022 artfynd.xlsx
+++ b/artfynd/A 5104-2022 artfynd.xlsx
@@ -1540,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868529</v>
+        <v>119868526</v>
       </c>
       <c r="B9" t="n">
-        <v>57316</v>
+        <v>57326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1580,17 +1580,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stor-Fänet, Sm</t>
+          <t>Stockemossen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584805</v>
+        <v>585167</v>
       </c>
       <c r="R9" t="n">
-        <v>6342764</v>
+        <v>6342782</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1660,10 +1660,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119868526</v>
+        <v>119868529</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>57316</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1700,17 +1700,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stockemossen, Sm</t>
+          <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585167</v>
+        <v>584805</v>
       </c>
       <c r="R10" t="n">
-        <v>6342782</v>
+        <v>6342764</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">

--- a/artfynd/A 5104-2022 artfynd.xlsx
+++ b/artfynd/A 5104-2022 artfynd.xlsx
@@ -1540,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868526</v>
+        <v>119868529</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>57316</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1580,17 +1580,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stockemossen, Sm</t>
+          <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585167</v>
+        <v>584805</v>
       </c>
       <c r="R9" t="n">
-        <v>6342782</v>
+        <v>6342764</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1660,10 +1660,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119868529</v>
+        <v>119868526</v>
       </c>
       <c r="B10" t="n">
-        <v>57316</v>
+        <v>57326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1700,17 +1700,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stor-Fänet, Sm</t>
+          <t>Stockemossen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584805</v>
+        <v>585167</v>
       </c>
       <c r="R10" t="n">
-        <v>6342764</v>
+        <v>6342782</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">

--- a/artfynd/A 5104-2022 artfynd.xlsx
+++ b/artfynd/A 5104-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119868373</v>
+        <v>119867064</v>
       </c>
       <c r="B2" t="n">
-        <v>56572</v>
+        <v>56218</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102976</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585031</v>
+        <v>585048</v>
       </c>
       <c r="R2" t="n">
-        <v>6342950</v>
+        <v>6342845</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119867109</v>
+        <v>119867065</v>
       </c>
       <c r="B3" t="n">
         <v>56223</v>
@@ -920,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119868495</v>
+        <v>119868526</v>
       </c>
       <c r="B4" t="n">
-        <v>57260</v>
+        <v>57326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,20 +937,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,29 +963,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-Fänet, Sm</t>
+          <t>Stockemossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584733</v>
+        <v>585167</v>
       </c>
       <c r="R4" t="n">
-        <v>6342643</v>
+        <v>6342782</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1034,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119867765</v>
+        <v>119868040</v>
       </c>
       <c r="B5" t="n">
-        <v>57679</v>
+        <v>57738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,45 +1057,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Fänet, Sm</t>
+          <t>Stockemossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584739</v>
+        <v>585249</v>
       </c>
       <c r="R5" t="n">
-        <v>6342593</v>
+        <v>6342792</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1124,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867108</v>
+        <v>119867765</v>
       </c>
       <c r="B6" t="n">
-        <v>56218</v>
+        <v>57679</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1208,21 +1208,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585048</v>
+        <v>584739</v>
       </c>
       <c r="R6" t="n">
-        <v>6342845</v>
+        <v>6342593</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1249,22 +1244,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,7 +1279,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1295,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119868372</v>
+        <v>119868495</v>
       </c>
       <c r="B7" t="n">
-        <v>56572</v>
+        <v>57260</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,20 +1302,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102976</v>
+        <v>102621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1333,19 +1328,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584948</v>
+        <v>584733</v>
       </c>
       <c r="R7" t="n">
-        <v>6342686</v>
+        <v>6342643</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,22 +1374,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,7 +1409,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1415,10 +1420,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868040</v>
+        <v>119868717</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>8421</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,50 +1432,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stockemossen, Sm</t>
+          <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585249</v>
+        <v>584752</v>
       </c>
       <c r="R8" t="n">
-        <v>6342792</v>
+        <v>6342618</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1494,22 +1499,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,7 +1534,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1540,10 +1545,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868529</v>
+        <v>119868373</v>
       </c>
       <c r="B9" t="n">
-        <v>57316</v>
+        <v>56572</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1552,20 +1557,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100048</v>
+        <v>102976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1575,7 +1580,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1584,13 +1589,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584805</v>
+        <v>585031</v>
       </c>
       <c r="R9" t="n">
-        <v>6342764</v>
+        <v>6342950</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1614,22 +1619,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1660,10 +1665,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119868526</v>
+        <v>119868372</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>56572</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1672,20 +1677,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>102976</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1700,17 +1705,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stockemossen, Sm</t>
+          <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585167</v>
+        <v>584948</v>
       </c>
       <c r="R10" t="n">
-        <v>6342782</v>
+        <v>6342686</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1734,22 +1739,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,10 +1785,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119868717</v>
+        <v>119868529</v>
       </c>
       <c r="B11" t="n">
-        <v>8421</v>
+        <v>57316</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1792,25 +1797,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1818,24 +1823,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584752</v>
+        <v>584805</v>
       </c>
       <c r="R11" t="n">
-        <v>6342618</v>
+        <v>6342764</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1859,22 +1859,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 5104-2022 artfynd.xlsx
+++ b/artfynd/A 5104-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119867064</v>
+        <v>119868372</v>
       </c>
       <c r="B2" t="n">
-        <v>56218</v>
+        <v>56572</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100092</v>
+        <v>102976</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585048</v>
+        <v>584948</v>
       </c>
       <c r="R2" t="n">
-        <v>6342845</v>
+        <v>6342686</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119867065</v>
+        <v>119868717</v>
       </c>
       <c r="B3" t="n">
-        <v>56223</v>
+        <v>8421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,9 +833,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>aktiv</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585050</v>
+        <v>584752</v>
       </c>
       <c r="R3" t="n">
-        <v>6342848</v>
+        <v>6342618</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119868526</v>
+        <v>119867108</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>56218</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +932,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -963,19 +958,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stockemossen, Sm</t>
+          <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585167</v>
+        <v>585048</v>
       </c>
       <c r="R4" t="n">
-        <v>6342782</v>
+        <v>6342845</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119868040</v>
+        <v>119868526</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>57326</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,31 +1061,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1094,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585249</v>
+        <v>585167</v>
       </c>
       <c r="R5" t="n">
-        <v>6342792</v>
+        <v>6342782</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1170,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867765</v>
+        <v>119868529</v>
       </c>
       <c r="B6" t="n">
-        <v>57679</v>
+        <v>57316</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,20 +1177,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1214,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584739</v>
+        <v>584805</v>
       </c>
       <c r="R6" t="n">
-        <v>6342593</v>
+        <v>6342764</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1249,7 +1244,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1259,7 +1254,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119868495</v>
+        <v>119868040</v>
       </c>
       <c r="B7" t="n">
-        <v>57260</v>
+        <v>57738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,52 +1297,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102621</v>
+        <v>103001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stor-Fänet, Sm</t>
+          <t>Stockemossen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584733</v>
+        <v>585249</v>
       </c>
       <c r="R7" t="n">
-        <v>6342643</v>
+        <v>6342792</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1379,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1389,7 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868717</v>
+        <v>119867065</v>
       </c>
       <c r="B8" t="n">
-        <v>8421</v>
+        <v>56223</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,21 +1426,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1458,9 +1448,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1469,13 +1459,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584752</v>
+        <v>585050</v>
       </c>
       <c r="R8" t="n">
-        <v>6342618</v>
+        <v>6342848</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,22 +1489,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1534,7 +1524,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1545,10 +1535,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868373</v>
+        <v>119868495</v>
       </c>
       <c r="B9" t="n">
-        <v>56572</v>
+        <v>57260</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1557,20 +1547,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102976</v>
+        <v>102621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1580,7 +1570,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585031</v>
+        <v>584733</v>
       </c>
       <c r="R9" t="n">
-        <v>6342950</v>
+        <v>6342643</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,22 +1619,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1665,7 +1665,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119868372</v>
+        <v>119868373</v>
       </c>
       <c r="B10" t="n">
         <v>56572</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584948</v>
+        <v>585031</v>
       </c>
       <c r="R10" t="n">
-        <v>6342686</v>
+        <v>6342950</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1739,22 +1739,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119868529</v>
+        <v>119867765</v>
       </c>
       <c r="B11" t="n">
-        <v>57316</v>
+        <v>57679</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1797,20 +1797,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584805</v>
+        <v>584739</v>
       </c>
       <c r="R11" t="n">
-        <v>6342764</v>
+        <v>6342593</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 5104-2022 artfynd.xlsx
+++ b/artfynd/A 5104-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119868372</v>
+        <v>119868717</v>
       </c>
       <c r="B2" t="n">
-        <v>56572</v>
+        <v>8421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102976</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,19 +713,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584948</v>
+        <v>584752</v>
       </c>
       <c r="R2" t="n">
-        <v>6342686</v>
+        <v>6342618</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119868717</v>
+        <v>119867108</v>
       </c>
       <c r="B3" t="n">
-        <v>8421</v>
+        <v>56218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,9 +838,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584752</v>
+        <v>585048</v>
       </c>
       <c r="R3" t="n">
-        <v>6342618</v>
+        <v>6342845</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -920,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119867108</v>
+        <v>119868372</v>
       </c>
       <c r="B4" t="n">
-        <v>56218</v>
+        <v>56572</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>102976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -958,21 +963,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585048</v>
+        <v>584948</v>
       </c>
       <c r="R4" t="n">
-        <v>6342845</v>
+        <v>6342686</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -999,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 5104-2022 artfynd.xlsx
+++ b/artfynd/A 5104-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119868717</v>
+        <v>119867152</v>
       </c>
       <c r="B2" t="n">
-        <v>8421</v>
+        <v>56218</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584752</v>
+        <v>585048</v>
       </c>
       <c r="R2" t="n">
-        <v>6342618</v>
+        <v>6342845</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119867108</v>
+        <v>119868373</v>
       </c>
       <c r="B3" t="n">
-        <v>56218</v>
+        <v>56572</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,35 +812,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>102976</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>aktiv</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585048</v>
+        <v>585031</v>
       </c>
       <c r="R3" t="n">
-        <v>6342845</v>
+        <v>6342950</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1045,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119868526</v>
+        <v>119868717</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>8421</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,25 +1052,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1083,19 +1078,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stockemossen, Sm</t>
+          <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585167</v>
+        <v>584752</v>
       </c>
       <c r="R5" t="n">
-        <v>6342782</v>
+        <v>6342618</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1165,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119868529</v>
+        <v>119867109</v>
       </c>
       <c r="B6" t="n">
-        <v>57316</v>
+        <v>56223</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,25 +1177,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>205995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1203,19 +1203,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584805</v>
+        <v>585050</v>
       </c>
       <c r="R6" t="n">
-        <v>6342764</v>
+        <v>6342848</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,22 +1244,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,7 +1279,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1410,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119867065</v>
+        <v>119867765</v>
       </c>
       <c r="B8" t="n">
-        <v>56223</v>
+        <v>57679</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,21 +1431,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1448,24 +1453,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585050</v>
+        <v>584739</v>
       </c>
       <c r="R8" t="n">
-        <v>6342848</v>
+        <v>6342593</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1535,10 +1535,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868495</v>
+        <v>119868526</v>
       </c>
       <c r="B9" t="n">
-        <v>57260</v>
+        <v>57326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1547,20 +1547,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1573,29 +1573,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stor-Fänet, Sm</t>
+          <t>Stockemossen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584733</v>
+        <v>585167</v>
       </c>
       <c r="R9" t="n">
-        <v>6342643</v>
+        <v>6342782</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,22 +1609,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,7 +1644,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1665,10 +1655,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119868373</v>
+        <v>119868495</v>
       </c>
       <c r="B10" t="n">
-        <v>56572</v>
+        <v>57260</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1677,20 +1667,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102976</v>
+        <v>102621</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1700,7 +1690,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585031</v>
+        <v>584733</v>
       </c>
       <c r="R10" t="n">
-        <v>6342950</v>
+        <v>6342643</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1739,22 +1739,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119867765</v>
+        <v>119868529</v>
       </c>
       <c r="B11" t="n">
-        <v>57679</v>
+        <v>57316</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1797,20 +1797,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584739</v>
+        <v>584805</v>
       </c>
       <c r="R11" t="n">
-        <v>6342593</v>
+        <v>6342764</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 5104-2022 artfynd.xlsx
+++ b/artfynd/A 5104-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119867152</v>
+        <v>119868526</v>
       </c>
       <c r="B2" t="n">
-        <v>56218</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100092</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +713,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stor-Fänet, Sm</t>
+          <t>Stockemossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585048</v>
+        <v>585167</v>
       </c>
       <c r="R2" t="n">
-        <v>6342845</v>
+        <v>6342782</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119868373</v>
+        <v>119867765</v>
       </c>
       <c r="B3" t="n">
-        <v>56572</v>
+        <v>57689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,20 +807,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102976</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585031</v>
+        <v>584739</v>
       </c>
       <c r="R3" t="n">
-        <v>6342950</v>
+        <v>6342593</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,7 +918,7 @@
         <v>119868372</v>
       </c>
       <c r="B4" t="n">
-        <v>56572</v>
+        <v>56582</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1040,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119868717</v>
+        <v>119867064</v>
       </c>
       <c r="B5" t="n">
-        <v>8421</v>
+        <v>56228</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,21 +1051,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1078,9 +1073,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1089,13 +1084,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584752</v>
+        <v>585048</v>
       </c>
       <c r="R5" t="n">
-        <v>6342618</v>
+        <v>6342845</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1114,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1149,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1165,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867109</v>
+        <v>119868529</v>
       </c>
       <c r="B6" t="n">
-        <v>56223</v>
+        <v>57326</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,25 +1172,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1203,24 +1198,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585050</v>
+        <v>584805</v>
       </c>
       <c r="R6" t="n">
-        <v>6342848</v>
+        <v>6342764</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,22 +1234,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,7 +1269,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1290,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119868040</v>
+        <v>119868373</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>56582</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,50 +1292,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>102976</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stockemossen, Sm</t>
+          <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585249</v>
+        <v>585031</v>
       </c>
       <c r="R7" t="n">
-        <v>6342792</v>
+        <v>6342950</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,22 +1354,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119867765</v>
+        <v>119867109</v>
       </c>
       <c r="B8" t="n">
-        <v>57679</v>
+        <v>56233</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,21 +1416,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1453,19 +1438,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584739</v>
+        <v>585050</v>
       </c>
       <c r="R8" t="n">
-        <v>6342593</v>
+        <v>6342848</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1489,22 +1479,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,7 +1514,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1535,10 +1525,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868526</v>
+        <v>119868040</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>57748</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1551,26 +1541,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1579,13 +1574,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585167</v>
+        <v>585249</v>
       </c>
       <c r="R9" t="n">
-        <v>6342782</v>
+        <v>6342792</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1609,22 +1604,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,7 +1639,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1658,7 +1653,7 @@
         <v>119868495</v>
       </c>
       <c r="B10" t="n">
-        <v>57260</v>
+        <v>57270</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1785,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119868529</v>
+        <v>119868717</v>
       </c>
       <c r="B11" t="n">
-        <v>57316</v>
+        <v>8421</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1797,25 +1792,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1823,19 +1818,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584805</v>
+        <v>584752</v>
       </c>
       <c r="R11" t="n">
-        <v>6342764</v>
+        <v>6342618</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1859,22 +1859,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 5104-2022 artfynd.xlsx
+++ b/artfynd/A 5104-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119868526</v>
+        <v>119868372</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>56582</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102976</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,17 +715,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stockemossen, Sm</t>
+          <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585167</v>
+        <v>584948</v>
       </c>
       <c r="R2" t="n">
-        <v>6342782</v>
+        <v>6342686</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119867765</v>
+        <v>119868040</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57748</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,45 +807,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stor-Fänet, Sm</t>
+          <t>Stockemossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584739</v>
+        <v>585249</v>
       </c>
       <c r="R3" t="n">
-        <v>6342593</v>
+        <v>6342792</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119868372</v>
+        <v>119867109</v>
       </c>
       <c r="B4" t="n">
-        <v>56582</v>
+        <v>56233</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,25 +932,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102976</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -953,19 +958,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584948</v>
+        <v>585050</v>
       </c>
       <c r="R4" t="n">
-        <v>6342686</v>
+        <v>6342848</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1034,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1035,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119867064</v>
+        <v>119868495</v>
       </c>
       <c r="B5" t="n">
-        <v>56228</v>
+        <v>57270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,21 +1061,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>102621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1073,9 +1083,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1084,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585048</v>
+        <v>584733</v>
       </c>
       <c r="R5" t="n">
-        <v>6342845</v>
+        <v>6342643</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,22 +1129,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1164,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1160,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119868529</v>
+        <v>119867152</v>
       </c>
       <c r="B6" t="n">
-        <v>57326</v>
+        <v>56228</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,25 +1187,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1198,16 +1213,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584805</v>
+        <v>585048</v>
       </c>
       <c r="R6" t="n">
-        <v>6342764</v>
+        <v>6342845</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1234,22 +1254,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1280,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119868373</v>
+        <v>119867765</v>
       </c>
       <c r="B7" t="n">
-        <v>56582</v>
+        <v>57689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,20 +1312,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102976</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1315,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1324,13 +1344,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585031</v>
+        <v>584739</v>
       </c>
       <c r="R7" t="n">
-        <v>6342950</v>
+        <v>6342593</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,22 +1374,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1420,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119867109</v>
+        <v>119868526</v>
       </c>
       <c r="B8" t="n">
-        <v>56233</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,25 +1432,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1438,21 +1458,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Fänet, Sm</t>
+          <t>Stockemossen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585050</v>
+        <v>585167</v>
       </c>
       <c r="R8" t="n">
-        <v>6342848</v>
+        <v>6342782</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1479,22 +1494,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,7 +1529,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1525,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868040</v>
+        <v>119868373</v>
       </c>
       <c r="B9" t="n">
-        <v>57748</v>
+        <v>56582</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,50 +1552,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103001</v>
+        <v>102976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stockemossen, Sm</t>
+          <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585249</v>
+        <v>585031</v>
       </c>
       <c r="R9" t="n">
-        <v>6342792</v>
+        <v>6342950</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1604,22 +1614,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1650,10 +1660,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119868495</v>
+        <v>119868529</v>
       </c>
       <c r="B10" t="n">
-        <v>57270</v>
+        <v>57326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1662,20 +1672,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102621</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1688,29 +1698,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584733</v>
+        <v>584805</v>
       </c>
       <c r="R10" t="n">
-        <v>6342643</v>
+        <v>6342764</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1734,22 +1734,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 5104-2022 artfynd.xlsx
+++ b/artfynd/A 5104-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119868372</v>
+        <v>119868526</v>
       </c>
       <c r="B2" t="n">
-        <v>56582</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102976</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,17 +715,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stor-Fänet, Sm</t>
+          <t>Stockemossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584948</v>
+        <v>585167</v>
       </c>
       <c r="R2" t="n">
-        <v>6342686</v>
+        <v>6342782</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119868040</v>
+        <v>119868529</v>
       </c>
       <c r="B3" t="n">
-        <v>57748</v>
+        <v>57326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,46 +811,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stockemossen, Sm</t>
+          <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585249</v>
+        <v>584805</v>
       </c>
       <c r="R3" t="n">
-        <v>6342792</v>
+        <v>6342764</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119867109</v>
+        <v>119867152</v>
       </c>
       <c r="B4" t="n">
-        <v>56233</v>
+        <v>56228</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,21 +931,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -969,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585050</v>
+        <v>585048</v>
       </c>
       <c r="R4" t="n">
-        <v>6342848</v>
+        <v>6342845</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119868495</v>
+        <v>119868717</v>
       </c>
       <c r="B5" t="n">
-        <v>57270</v>
+        <v>8421</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,21 +1056,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102621</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1083,14 +1078,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1099,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584733</v>
+        <v>584752</v>
       </c>
       <c r="R5" t="n">
-        <v>6342643</v>
+        <v>6342618</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1175,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867152</v>
+        <v>119867065</v>
       </c>
       <c r="B6" t="n">
-        <v>56228</v>
+        <v>56233</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1181,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1224,13 +1214,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585048</v>
+        <v>585050</v>
       </c>
       <c r="R6" t="n">
-        <v>6342845</v>
+        <v>6342848</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,7 +1249,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1259,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119867765</v>
+        <v>119868495</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57270</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,16 +1306,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>102621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1338,19 +1328,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584739</v>
+        <v>584733</v>
       </c>
       <c r="R7" t="n">
-        <v>6342593</v>
+        <v>6342643</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,22 +1374,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,10 +1420,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868526</v>
+        <v>119868040</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>57748</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1436,26 +1436,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1464,13 +1469,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585167</v>
+        <v>585249</v>
       </c>
       <c r="R8" t="n">
-        <v>6342782</v>
+        <v>6342792</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1494,22 +1499,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,7 +1534,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1540,7 +1545,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868373</v>
+        <v>119868372</v>
       </c>
       <c r="B9" t="n">
         <v>56582</v>
@@ -1575,7 +1580,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1584,13 +1589,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585031</v>
+        <v>584948</v>
       </c>
       <c r="R9" t="n">
-        <v>6342950</v>
+        <v>6342686</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1614,22 +1619,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,7 +1654,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1660,10 +1665,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119868529</v>
+        <v>119867765</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>57689</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1672,20 +1677,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1704,10 +1709,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584805</v>
+        <v>584739</v>
       </c>
       <c r="R10" t="n">
-        <v>6342764</v>
+        <v>6342593</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1739,7 +1744,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1754,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,10 +1785,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119868717</v>
+        <v>119868373</v>
       </c>
       <c r="B11" t="n">
-        <v>8421</v>
+        <v>56582</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1792,35 +1797,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>102976</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584752</v>
+        <v>585031</v>
       </c>
       <c r="R11" t="n">
-        <v>6342618</v>
+        <v>6342950</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1859,22 +1859,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 5104-2022 artfynd.xlsx
+++ b/artfynd/A 5104-2022 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119867065</v>
+        <v>119868495</v>
       </c>
       <c r="B6" t="n">
-        <v>56233</v>
+        <v>57270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1203,9 +1203,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1214,13 +1219,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585050</v>
+        <v>584733</v>
       </c>
       <c r="R6" t="n">
-        <v>6342848</v>
+        <v>6342643</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,22 +1249,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,7 +1284,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1290,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119868495</v>
+        <v>119867065</v>
       </c>
       <c r="B7" t="n">
-        <v>57270</v>
+        <v>56233</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,21 +1311,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102621</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1328,14 +1333,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1344,13 +1344,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584733</v>
+        <v>585050</v>
       </c>
       <c r="R7" t="n">
-        <v>6342643</v>
+        <v>6342848</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,22 +1374,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 5104-2022 artfynd.xlsx
+++ b/artfynd/A 5104-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119868526</v>
+        <v>119867153</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>56233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>205995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stockemossen, Sm</t>
+          <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585167</v>
+        <v>585050</v>
       </c>
       <c r="R2" t="n">
-        <v>6342782</v>
+        <v>6342848</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -749,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -915,7 +920,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119867152</v>
+        <v>119867064</v>
       </c>
       <c r="B4" t="n">
         <v>56228</v>
@@ -1165,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119868495</v>
+        <v>119868040</v>
       </c>
       <c r="B6" t="n">
-        <v>57270</v>
+        <v>57748</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,52 +1182,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102621</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stor-Fänet, Sm</t>
+          <t>Stockemossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584733</v>
+        <v>585249</v>
       </c>
       <c r="R6" t="n">
-        <v>6342643</v>
+        <v>6342792</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119867065</v>
+        <v>119868372</v>
       </c>
       <c r="B7" t="n">
-        <v>56233</v>
+        <v>56582</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,25 +1307,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>102976</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1333,24 +1333,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585050</v>
+        <v>584948</v>
       </c>
       <c r="R7" t="n">
-        <v>6342848</v>
+        <v>6342686</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,22 +1369,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,7 +1404,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1420,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868040</v>
+        <v>119868495</v>
       </c>
       <c r="B8" t="n">
-        <v>57748</v>
+        <v>57270</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1432,47 +1427,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>102621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stockemossen, Sm</t>
+          <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585249</v>
+        <v>584733</v>
       </c>
       <c r="R8" t="n">
-        <v>6342792</v>
+        <v>6342643</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,10 +1545,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119868372</v>
+        <v>119867765</v>
       </c>
       <c r="B9" t="n">
-        <v>56582</v>
+        <v>57689</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1557,20 +1557,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102976</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584948</v>
+        <v>584739</v>
       </c>
       <c r="R9" t="n">
-        <v>6342686</v>
+        <v>6342593</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1619,22 +1619,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1665,10 +1665,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119867765</v>
+        <v>119868526</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1705,17 +1705,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stor-Fänet, Sm</t>
+          <t>Stockemossen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584739</v>
+        <v>585167</v>
       </c>
       <c r="R10" t="n">
-        <v>6342593</v>
+        <v>6342782</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">

--- a/artfynd/A 5104-2022 artfynd.xlsx
+++ b/artfynd/A 5104-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119867153</v>
+        <v>119867765</v>
       </c>
       <c r="B2" t="n">
-        <v>56233</v>
+        <v>57689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +713,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585050</v>
+        <v>584739</v>
       </c>
       <c r="R2" t="n">
-        <v>6342848</v>
+        <v>6342593</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119868529</v>
+        <v>119868526</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -840,17 +835,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stor-Fänet, Sm</t>
+          <t>Stockemossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584805</v>
+        <v>585167</v>
       </c>
       <c r="R3" t="n">
-        <v>6342764</v>
+        <v>6342782</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +904,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -920,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119867064</v>
+        <v>119867109</v>
       </c>
       <c r="B4" t="n">
-        <v>56228</v>
+        <v>56233</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,21 +931,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -969,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585048</v>
+        <v>585050</v>
       </c>
       <c r="R4" t="n">
-        <v>6342845</v>
+        <v>6342848</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119868717</v>
+        <v>119868529</v>
       </c>
       <c r="B5" t="n">
-        <v>8421</v>
+        <v>57326</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,25 +1052,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1083,24 +1078,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584752</v>
+        <v>584805</v>
       </c>
       <c r="R5" t="n">
-        <v>6342618</v>
+        <v>6342764</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1114,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1149,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1170,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119868040</v>
+        <v>119867152</v>
       </c>
       <c r="B6" t="n">
-        <v>57748</v>
+        <v>56228</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,50 +1172,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stockemossen, Sm</t>
+          <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585249</v>
+        <v>585048</v>
       </c>
       <c r="R6" t="n">
-        <v>6342792</v>
+        <v>6342845</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,22 +1239,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,7 +1274,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1415,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119868495</v>
+        <v>119868373</v>
       </c>
       <c r="B8" t="n">
-        <v>57270</v>
+        <v>56582</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,20 +1417,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102621</v>
+        <v>102976</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1450,17 +1440,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1469,13 +1449,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584733</v>
+        <v>585031</v>
       </c>
       <c r="R8" t="n">
-        <v>6342643</v>
+        <v>6342950</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,22 +1479,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,10 +1525,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119867765</v>
+        <v>119868717</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>8421</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1561,21 +1541,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1583,19 +1563,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584739</v>
+        <v>584752</v>
       </c>
       <c r="R9" t="n">
-        <v>6342593</v>
+        <v>6342618</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,22 +1604,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,7 +1639,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1665,10 +1650,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119868526</v>
+        <v>119868495</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>57270</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1677,20 +1662,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>102621</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1703,19 +1688,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stockemossen, Sm</t>
+          <t>Stor-Fänet, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585167</v>
+        <v>584733</v>
       </c>
       <c r="R10" t="n">
-        <v>6342782</v>
+        <v>6342643</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1739,22 +1734,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,7 +1769,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1785,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119868373</v>
+        <v>119868040</v>
       </c>
       <c r="B11" t="n">
-        <v>56582</v>
+        <v>57748</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1797,45 +1792,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102976</v>
+        <v>103001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stor-Fänet, Sm</t>
+          <t>Stockemossen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585031</v>
+        <v>585249</v>
       </c>
       <c r="R11" t="n">
-        <v>6342950</v>
+        <v>6342792</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1859,22 +1859,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
